--- a/data/trans_dic/POLIPATOLOGIA_Lim_5-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_Lim_5-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante</t>
+          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,45; 11,35</t>
+          <t>7,41; 11,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,13; 9,9</t>
+          <t>6,25; 9,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,37; 23,54</t>
+          <t>17,54; 23,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,97; 21,45</t>
+          <t>17,05; 21,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,13; 22,55</t>
+          <t>17,13; 22,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,53; 38,06</t>
+          <t>32,37; 37,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,33; 16,5</t>
+          <t>13,45; 16,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,87; 16,39</t>
+          <t>12,81; 16,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27,12; 31,51</t>
+          <t>27,21; 31,39</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,88</t>
+          <t>0,89; 1,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,42</t>
+          <t>1,19; 2,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,3; 5,73</t>
+          <t>3,24; 5,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,72; 4,67</t>
+          <t>2,73; 4,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,28; 6,43</t>
+          <t>4,33; 6,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,48; 10,47</t>
+          <t>6,5; 10,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 3,02</t>
+          <t>1,9; 2,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,9; 4,07</t>
+          <t>2,83; 4,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,42; 7,83</t>
+          <t>5,56; 7,74</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,0</t>
+          <t>0,41; 3,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,79</t>
+          <t>0,93; 3,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,67</t>
+          <t>1,52; 3,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,68</t>
+          <t>1,29; 4,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,86</t>
+          <t>1,71; 5,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,19; 9,74</t>
+          <t>6,17; 9,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 3,27</t>
+          <t>1,08; 3,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,72</t>
+          <t>1,62; 3,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,13; 6,17</t>
+          <t>4,11; 6,15</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,0; 4,34</t>
+          <t>2,97; 4,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,57; 3,8</t>
+          <t>2,61; 3,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,09; 7,63</t>
+          <t>5,2; 7,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,33; 10,38</t>
+          <t>8,31; 10,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,01; 10,01</t>
+          <t>7,96; 9,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,37; 15,48</t>
+          <t>11,5; 15,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,87; 7,12</t>
+          <t>5,89; 7,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,46; 6,72</t>
+          <t>5,51; 6,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,22; 11,42</t>
+          <t>9,01; 11,43</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante</t>
+          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>72621; 110635</t>
+          <t>72224; 110982</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>46210; 74690</t>
+          <t>47134; 74145</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>89421; 121213</t>
+          <t>90327; 121998</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>227015; 287003</t>
+          <t>228122; 287255</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>170411; 224314</t>
+          <t>170394; 222085</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>245797; 287559</t>
+          <t>244563; 286106</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>308357; 381561</t>
+          <t>311038; 380209</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>225175; 286718</t>
+          <t>224110; 287131</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>344582; 400275</t>
+          <t>345652; 398842</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17353; 37009</t>
+          <t>17461; 38393</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25625; 50195</t>
+          <t>24788; 49880</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>75684; 131136</t>
+          <t>74168; 132127</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47878; 82050</t>
+          <t>48024; 83253</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>85078; 127895</t>
+          <t>86178; 130783</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>144983; 234352</t>
+          <t>145539; 233386</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>70350; 112351</t>
+          <t>70829; 109940</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>117911; 165494</t>
+          <t>115000; 164720</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>245458; 354337</t>
+          <t>251977; 350575</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1953; 14421</t>
+          <t>1951; 15295</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5585; 20718</t>
+          <t>5113; 19727</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9479; 23700</t>
+          <t>9845; 25106</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5924; 21473</t>
+          <t>5906; 20955</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9064; 26694</t>
+          <t>9375; 27878</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>40897; 64330</t>
+          <t>40783; 63761</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10039; 30750</t>
+          <t>10131; 29942</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17253; 40822</t>
+          <t>17760; 41190</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>53963; 80676</t>
+          <t>53720; 80415</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>102545; 148347</t>
+          <t>101568; 146968</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>86909; 128270</t>
+          <t>88014; 126840</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>175782; 263310</t>
+          <t>179574; 259704</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>295958; 368998</t>
+          <t>295471; 366084</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>282941; 353645</t>
+          <t>281104; 351057</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>415294; 565516</t>
+          <t>420082; 565321</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>409661; 496641</t>
+          <t>410457; 497413</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>377100; 464667</t>
+          <t>380597; 465165</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>654889; 811403</t>
+          <t>640429; 811943</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/POLIPATOLOGIA_Lim_5-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_Lim_5-Estudios-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>28,22%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,41; 11,39</t>
+          <t>7,49; 11,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,25; 9,83</t>
+          <t>6,32; 9,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,54; 23,69</t>
+          <t>16,87; 22,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,05; 21,47</t>
+          <t>16,98; 21,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,13; 22,33</t>
+          <t>17,05; 22,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,37; 37,87</t>
+          <t>32,09; 37,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,45; 16,44</t>
+          <t>13,44; 16,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,81; 16,42</t>
+          <t>12,87; 16,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27,21; 31,39</t>
+          <t>26,24; 30,3</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,95</t>
+          <t>0,82; 1,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,4</t>
+          <t>1,16; 2,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,24; 5,77</t>
+          <t>4,37; 6,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,73; 4,74</t>
+          <t>2,71; 4,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,33; 6,58</t>
+          <t>4,26; 6,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,5; 10,43</t>
+          <t>9,11; 11,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,9; 2,95</t>
+          <t>1,9; 2,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 4,05</t>
+          <t>2,82; 4,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,56; 7,74</t>
+          <t>7,04; 8,36</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,18</t>
+          <t>0,41; 3,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,61</t>
+          <t>0,95; 3,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,88</t>
+          <t>1,5; 3,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,57</t>
+          <t>1,41; 4,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 5,08</t>
+          <t>1,66; 5,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,17; 9,65</t>
+          <t>6,25; 9,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,19</t>
+          <t>1,04; 3,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,76</t>
+          <t>1,53; 3,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,11; 6,15</t>
+          <t>4,22; 6,16</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,97; 4,3</t>
+          <t>2,95; 4,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,61; 3,76</t>
+          <t>2,64; 3,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,2; 7,52</t>
+          <t>6,2; 7,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,31; 10,3</t>
+          <t>8,37; 10,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,96; 9,94</t>
+          <t>8,01; 10,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,5; 15,47</t>
+          <t>14,13; 16,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,89; 7,13</t>
+          <t>5,88; 7,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,51; 6,73</t>
+          <t>5,57; 6,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,01; 11,43</t>
+          <t>10,51; 11,8</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>105379</t>
+          <t>112067</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>265780</t>
+          <t>283241</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>371159</t>
+          <t>395308</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>72224; 110982</t>
+          <t>73012; 109925</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>47134; 74145</t>
+          <t>47711; 74647</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>90327; 121998</t>
+          <t>97577; 132747</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>228122; 287255</t>
+          <t>227095; 285265</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>170394; 222085</t>
+          <t>169581; 224000</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>244563; 286106</t>
+          <t>263762; 304123</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>311038; 380209</t>
+          <t>310855; 386832</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>224110; 287131</t>
+          <t>225134; 286785</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>345652; 398842</t>
+          <t>367531; 424330</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>108625</t>
+          <t>116543</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>199953</t>
+          <t>219879</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>308578</t>
+          <t>336423</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17461; 38393</t>
+          <t>16141; 36618</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24788; 49880</t>
+          <t>24030; 49378</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74168; 132127</t>
+          <t>97480; 137252</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>48024; 83253</t>
+          <t>47689; 81940</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>86178; 130783</t>
+          <t>84783; 126054</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>145539; 233386</t>
+          <t>197763; 243963</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>70829; 109940</t>
+          <t>70815; 109516</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>115000; 164720</t>
+          <t>114651; 165941</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>251977; 350575</t>
+          <t>309717; 368015</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15907</t>
+          <t>17423</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50518</t>
+          <t>57183</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>66425</t>
+          <t>74605</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1951; 15295</t>
+          <t>1984; 18009</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5113; 19727</t>
+          <t>5212; 20459</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9845; 25106</t>
+          <t>10676; 27752</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5906; 20955</t>
+          <t>6453; 21950</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9375; 27878</t>
+          <t>9138; 27959</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>40783; 63761</t>
+          <t>45947; 70379</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10131; 29942</t>
+          <t>9789; 29437</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17760; 41190</t>
+          <t>16802; 39970</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>53720; 80415</t>
+          <t>61071; 89079</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>229911</t>
+          <t>246033</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>516251</t>
+          <t>560303</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>746162</t>
+          <t>806336</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>101568; 146968</t>
+          <t>100733; 146548</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>88014; 126840</t>
+          <t>89022; 127751</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>179574; 259704</t>
+          <t>218383; 277044</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>295471; 366084</t>
+          <t>297589; 366391</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>281104; 351057</t>
+          <t>283021; 354811</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>420082; 565321</t>
+          <t>526935; 597066</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>410457; 497413</t>
+          <t>409917; 496284</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>380597; 465165</t>
+          <t>384670; 465375</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>640429; 811943</t>
+          <t>761804; 855725</t>
         </is>
       </c>
     </row>
